--- a/Feedback_RP's.xlsx
+++ b/Feedback_RP's.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Sl.No</t>
   </si>
@@ -69,13 +69,28 @@
     <t>Q-upload for text book and Text book page</t>
   </si>
   <si>
-    <t>Reference link for refresh</t>
-  </si>
-  <si>
     <t>Textbook and textbook page should be put in dropdown</t>
   </si>
   <si>
     <t>Sessions-1</t>
+  </si>
+  <si>
+    <t>how to avoid duplicate</t>
+  </si>
+  <si>
+    <t>Curricular Goal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objective </t>
+  </si>
+  <si>
+    <t>Short answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limited Reject threshold up-to 2-3 times </t>
+  </si>
+  <si>
+    <t>Reference link</t>
   </si>
 </sst>
 </file>
@@ -99,7 +114,7 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -180,9 +195,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -213,6 +225,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -508,45 +523,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="33.77734375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="45" style="6" customWidth="1"/>
-    <col min="4" max="4" width="34.88671875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="33.77734375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="45" style="5" customWidth="1"/>
+    <col min="4" max="4" width="34.88671875" style="6" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.8">
+    <row r="1" spans="1:4" ht="18">
       <c r="A1" s="1"/>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="4" t="s">
-        <v>19</v>
+      <c r="C1" s="14"/>
+      <c r="D1" s="15" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18">
       <c r="A2" s="1"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="8">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="7">
         <v>46146</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="13" customFormat="1" ht="18">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:4" s="12" customFormat="1" ht="18">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>4</v>
       </c>
     </row>
@@ -554,13 +569,13 @@
       <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -568,13 +583,13 @@
       <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -582,59 +597,99 @@
       <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="9"/>
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="8"/>
     </row>
     <row r="7" spans="1:4" ht="18">
       <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:4" ht="36">
       <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="9"/>
+      <c r="D8" s="8"/>
     </row>
     <row r="9" spans="1:4" ht="36">
       <c r="A9" s="3">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="9"/>
+      <c r="C9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="8"/>
     </row>
     <row r="10" spans="1:4" ht="18">
       <c r="A10" s="3">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="8"/>
+    </row>
+    <row r="11" spans="1:4" ht="18">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:4" ht="18">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" spans="1:4" ht="18">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:4" ht="18">
+      <c r="A14" s="3">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
